--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N121_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N121_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90153602546194</v>
+        <v>12.49649960413756</v>
       </c>
       <c r="D2" t="n">
-        <v>19.27182792832082</v>
+        <v>3.131672038352134</v>
       </c>
       <c r="E2" t="n">
-        <v>24.29117950274327</v>
+        <v>3.947316669195781</v>
       </c>
       <c r="F2" t="n">
-        <v>10.45695450277603</v>
+        <v>1.699255106701105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.56458506529852</v>
+        <v>11.30424507311101</v>
       </c>
       <c r="D3" t="n">
-        <v>26.87347492843286</v>
+        <v>4.36693967587034</v>
       </c>
       <c r="E3" t="n">
-        <v>24.29117950274327</v>
+        <v>3.947316669195781</v>
       </c>
       <c r="F3" t="n">
-        <v>10.45695450277603</v>
+        <v>1.699255106701105</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.84893687644119</v>
+        <v>7.450452242421695</v>
       </c>
       <c r="D4" t="n">
-        <v>45.13745028715221</v>
+        <v>7.334835671662235</v>
       </c>
       <c r="E4" t="n">
-        <v>24.29117950274327</v>
+        <v>3.947316669195781</v>
       </c>
       <c r="F4" t="n">
-        <v>10.45695450277603</v>
+        <v>1.699255106701105</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.67752689025354</v>
+        <v>2.385098119666199</v>
       </c>
       <c r="D5" t="n">
-        <v>14.95640535354355</v>
+        <v>2.430415869950826</v>
       </c>
       <c r="E5" t="n">
-        <v>24.29117950274327</v>
+        <v>3.947316669195781</v>
       </c>
       <c r="F5" t="n">
-        <v>10.45695450277603</v>
+        <v>1.699255106701105</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.56458022384778</v>
+        <v>3.991744286375265</v>
       </c>
       <c r="D6" t="n">
-        <v>30.70688212613786</v>
+        <v>4.989868345497403</v>
       </c>
       <c r="E6" t="n">
-        <v>24.29117950274327</v>
+        <v>3.947316669195781</v>
       </c>
       <c r="F6" t="n">
-        <v>10.45695450277603</v>
+        <v>1.699255106701105</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
